--- a/project/2025_KDT_해커톤_개요.xlsx
+++ b/project/2025_KDT_해커톤_개요.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI-X\project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai_x\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AD018A-D547-4A9D-8514-BDF7C27C3F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,21 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="182">
   <si>
     <t>구분</t>
   </si>
@@ -352,9 +344,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>듀오블룸 - 난임부부 종합 케어(정책, 의료, 멘탈헬스) 서비스</t>
-  </si>
-  <si>
     <t>밥상일터 - AI 기반으로 고령층에게 맞춤형 소일거리를 추천하고, 이를 통해 얻은 보상을 식사로 교환할 수 있도록 지원</t>
   </si>
   <si>
@@ -395,9 +384,6 @@
   </si>
   <si>
     <t>청사진(靑史進) - 청년 자산관리 및 미래설계 플랫폼</t>
-  </si>
-  <si>
-    <t>바른말싸미 - 초등학생들의 비속어 사용을 실시간으로 감지하고 교정함으로써, 사이버 폭력의 발생을 줄이는 데 기여</t>
   </si>
   <si>
     <t>RAG 기반 보고서 생성 어시스턴트 - ESG경영이 어려운 중소기업을 위해 실제 사례와 최신 데이터가 반영된 ESG보고서를 생성하여 중소기업의 ESG경영을 지원</t>
@@ -606,14 +592,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>자유과제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지정과제 - 지역격차 해소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2. 의료/복지 격차 해소</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -639,13 +617,25 @@
   </si>
   <si>
     <t>- AI 수요예측 기반 맞춤형 대중교통 서비스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지정과제 - 지역 균형발전 -&gt; 지역격차 해소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>듀오블룸 - 난임부부 종합 케어(정책, 의료, 멘탈헬스) 서비스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바른말싸미 - 초등학생들의 비속어 사용을 실시간으로 감지하고 교정함으로써, 사이버 폭력의 발생을 줄이는 데 기여</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -850,7 +840,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -878,60 +868,117 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -946,78 +993,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1332,940 +1307,922 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H84"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.75" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.75" style="10"/>
-    <col min="3" max="3" width="17.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.69921875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.69921875" style="9"/>
+    <col min="3" max="3" width="17.8984375" style="2" customWidth="1"/>
     <col min="4" max="4" width="25.5" style="2" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="87.25" style="3" customWidth="1"/>
-    <col min="6" max="6" width="1.375" style="3" customWidth="1"/>
-    <col min="7" max="8" width="49.875" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="8.75" style="4"/>
+    <col min="5" max="5" width="87.19921875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="1.3984375" style="3" customWidth="1"/>
+    <col min="7" max="8" width="49.8984375" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="8.69921875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
       <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="46" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B3" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="48"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="47" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="11"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B4" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B5" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B6" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="48"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B7" s="47" t="s">
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B7" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B8" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B10" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="48"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="47" t="s">
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B11" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="48"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="46" t="s">
+      <c r="D11" s="24"/>
+      <c r="E11" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="48"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B11" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="41" t="s">
+      <c r="F11" s="11"/>
+      <c r="G11" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="H11" s="34"/>
+    </row>
+    <row r="12" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="41" t="s">
+      <c r="D12" s="5"/>
+      <c r="E12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B13" s="36"/>
+      <c r="C13" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="38" t="s">
+      <c r="D13" s="5"/>
+      <c r="E13" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B14" s="36"/>
+      <c r="C14" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="31"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="6"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="H15" s="30"/>
+    </row>
+    <row r="16" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H16" s="31"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B17" s="36"/>
+      <c r="C17" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" s="30"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="36"/>
+      <c r="C18" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G18" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="H11" s="38"/>
-    </row>
-    <row r="12" spans="2:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="17" t="s">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B19" s="36"/>
+      <c r="C19" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="52" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="9" t="s">
+      <c r="D19" s="5"/>
+      <c r="E19" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B20" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="G20" s="32" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="50"/>
-      <c r="C13" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="9" t="s">
+      <c r="H20" s="31"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B22" s="10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="38"/>
+      <c r="H23" s="25" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B24" s="18">
+        <v>6</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="G24" s="46"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B25" s="18">
+        <v>6</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="H13" s="54" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="50"/>
-      <c r="C14" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="55" t="s">
-        <v>179</v>
-      </c>
-      <c r="H14" s="53"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B15" s="50"/>
-      <c r="C15" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="54" t="s">
-        <v>181</v>
-      </c>
-      <c r="H15" s="52" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="H16" s="53"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="50"/>
-      <c r="C17" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="54" t="s">
-        <v>170</v>
-      </c>
-      <c r="H17" s="52"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="54" t="s">
-        <v>171</v>
-      </c>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="50"/>
-      <c r="C19" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="53" t="s">
-        <v>177</v>
-      </c>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="54" t="s">
-        <v>182</v>
-      </c>
-      <c r="H20" s="53"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="F23" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="44"/>
-      <c r="H23" s="45" t="s">
+      <c r="F25" s="47"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="13"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B26" s="18">
+        <v>6</v>
+      </c>
+      <c r="C26" s="18" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="B24" s="35">
-        <v>6</v>
-      </c>
-      <c r="C24" s="35" t="s">
+      <c r="D26" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" s="47"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="13"/>
+    </row>
+    <row r="27" spans="1:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B27" s="15">
+        <v>6</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="D24" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="G24" s="27"/>
-      <c r="H24" s="24"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="35">
-        <v>6</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="25"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="35">
-        <v>6</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" s="28"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="25"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="32">
-        <v>6</v>
-      </c>
-      <c r="C27" s="32" t="s">
+      <c r="D27" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="47"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="13"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B28" s="15">
+        <v>6</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="47"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="13"/>
+    </row>
+    <row r="29" spans="1:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B29" s="15">
+        <v>6</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F29" s="47"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="13"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B30" s="15">
+        <v>6</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="47"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="13"/>
+    </row>
+    <row r="31" spans="1:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B31" s="5">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="28"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="25"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="32">
-        <v>6</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="28"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="25"/>
-    </row>
-    <row r="29" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="B29" s="32">
-        <v>6</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="25"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="32">
-        <v>6</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="F30" s="28"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="25"/>
-    </row>
-    <row r="31" spans="1:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="B31" s="5">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>87</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F31" s="28"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="25"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="F31" s="47"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="13"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B32" s="5">
         <v>6</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>77</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F32" s="28"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="25"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="F32" s="47"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="13"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B33" s="5">
         <v>6</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F33" s="28"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="25"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="F33" s="47"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="13"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B34" s="5">
         <v>6</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>79</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F34" s="28"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="25"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="F34" s="47"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="13"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B35" s="5">
         <v>6</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>80</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F35" s="28"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="25"/>
-    </row>
-    <row r="36" spans="2:8" ht="27" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="F35" s="47"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="13"/>
+    </row>
+    <row r="36" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B36" s="5">
         <v>6</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>83</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="25"/>
-    </row>
-    <row r="37" spans="2:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="F36" s="47"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="13"/>
+    </row>
+    <row r="37" spans="2:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B37" s="5">
         <v>6</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>81</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="F37" s="28"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="25"/>
-    </row>
-    <row r="38" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="F37" s="47"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="13"/>
+    </row>
+    <row r="38" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="5">
         <v>6</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>74</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F38" s="30"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="26"/>
-    </row>
-    <row r="39" spans="2:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="B39" s="35">
-        <v>6</v>
-      </c>
-      <c r="C39" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="D39" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="F38" s="49"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="14"/>
+    </row>
+    <row r="39" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B39" s="18">
+        <v>6</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D39" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E39" s="36" t="s">
+      <c r="E39" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="F39" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="G39" s="40"/>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B40" s="18">
+        <v>6</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F40" s="41"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="13"/>
+    </row>
+    <row r="41" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B41" s="15">
+        <v>6</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E41" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F39" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="G39" s="19"/>
-      <c r="H39" s="24"/>
-    </row>
-    <row r="40" spans="2:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="B40" s="35">
-        <v>6</v>
-      </c>
-      <c r="C40" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="D40" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="25"/>
-    </row>
-    <row r="41" spans="2:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="B41" s="32">
-        <v>6</v>
-      </c>
-      <c r="C41" s="32" t="s">
+      <c r="F41" s="41"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="13"/>
+    </row>
+    <row r="42" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B42" s="15">
+        <v>6</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F42" s="41"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="13"/>
+    </row>
+    <row r="43" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B43" s="15">
+        <v>6</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F43" s="41"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="13"/>
+    </row>
+    <row r="44" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B44" s="5">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="E41" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="25"/>
-    </row>
-    <row r="42" spans="2:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="32">
-        <v>6</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="E42" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="F42" s="20"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="25"/>
-    </row>
-    <row r="43" spans="2:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="B43" s="32">
-        <v>6</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="E43" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="25"/>
-    </row>
-    <row r="44" spans="2:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="B44" s="5">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>90</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F44" s="20"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="25"/>
-    </row>
-    <row r="45" spans="2:8" ht="27" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+      <c r="F44" s="41"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="13"/>
+    </row>
+    <row r="45" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B45" s="5">
         <v>6</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>94</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="F45" s="20"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="25"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+      <c r="F45" s="41"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="13"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B46" s="5">
         <v>6</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>92</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F46" s="20"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="25"/>
-    </row>
-    <row r="47" spans="2:8" ht="27" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="F46" s="41"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="13"/>
+    </row>
+    <row r="47" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B47" s="5">
         <v>6</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>100</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="F47" s="20"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="25"/>
-    </row>
-    <row r="48" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+      <c r="F47" s="41"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="13"/>
+    </row>
+    <row r="48" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B48" s="5">
         <v>6</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>96</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="F48" s="20"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="25"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+      <c r="F48" s="41"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="13"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B49" s="5">
         <v>6</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>97</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="25"/>
-    </row>
-    <row r="50" spans="2:8" ht="27" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="F49" s="41"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="13"/>
+    </row>
+    <row r="50" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B50" s="5">
         <v>6</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>99</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F50" s="20"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="25"/>
-    </row>
-    <row r="51" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+      <c r="F50" s="41"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="13"/>
+    </row>
+    <row r="51" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B51" s="5">
         <v>6</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>88</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F51" s="20"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="25"/>
-    </row>
-    <row r="52" spans="2:8" ht="27" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+      <c r="F51" s="41"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="13"/>
+    </row>
+    <row r="52" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
       <c r="B52" s="5">
         <v>6</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>101</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="25"/>
-    </row>
-    <row r="53" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="F52" s="41"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="13"/>
+    </row>
+    <row r="53" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B53" s="5">
         <v>6</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>102</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="F53" s="22"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="26"/>
-    </row>
-    <row r="54" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="35">
+        <v>130</v>
+      </c>
+      <c r="F53" s="43"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="14"/>
+    </row>
+    <row r="54" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="18">
         <v>5</v>
       </c>
-      <c r="C54" s="36" t="s">
+      <c r="C54" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D54" s="37" t="s">
+      <c r="D54" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E54" s="36" t="s">
+      <c r="E54" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="G54" s="19"/>
-      <c r="H54" s="24"/>
-    </row>
-    <row r="55" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="35">
+      <c r="F54" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="G54" s="40"/>
+      <c r="H54" s="12"/>
+    </row>
+    <row r="55" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B55" s="18">
         <v>5</v>
       </c>
-      <c r="C55" s="36" t="s">
+      <c r="C55" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D55" s="37" t="s">
+      <c r="D55" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E55" s="36" t="s">
+      <c r="E55" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F55" s="20"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="25"/>
-    </row>
-    <row r="56" spans="2:8" ht="27" x14ac:dyDescent="0.3">
-      <c r="B56" s="35">
+      <c r="F55" s="41"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="13"/>
+    </row>
+    <row r="56" spans="2:8" ht="31.2" x14ac:dyDescent="0.4">
+      <c r="B56" s="18">
         <v>5</v>
       </c>
-      <c r="C56" s="36" t="s">
+      <c r="C56" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="D56" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="E56" s="36" t="s">
+      <c r="E56" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="F56" s="20"/>
-      <c r="G56" s="21"/>
-      <c r="H56" s="25"/>
-    </row>
-    <row r="57" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="32">
+      <c r="F56" s="41"/>
+      <c r="G56" s="42"/>
+      <c r="H56" s="13"/>
+    </row>
+    <row r="57" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B57" s="15">
         <v>5</v>
       </c>
-      <c r="C57" s="33" t="s">
+      <c r="C57" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D57" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E57" s="33" t="s">
+      <c r="E57" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F57" s="20"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="25"/>
-    </row>
-    <row r="58" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="32">
+      <c r="F57" s="41"/>
+      <c r="G57" s="42"/>
+      <c r="H57" s="13"/>
+    </row>
+    <row r="58" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B58" s="15">
         <v>5</v>
       </c>
-      <c r="C58" s="33" t="s">
+      <c r="C58" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D58" s="34" t="s">
+      <c r="D58" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E58" s="33" t="s">
+      <c r="E58" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F58" s="20"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="25"/>
-    </row>
-    <row r="59" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="32">
+      <c r="F58" s="41"/>
+      <c r="G58" s="42"/>
+      <c r="H58" s="13"/>
+    </row>
+    <row r="59" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B59" s="15">
         <v>5</v>
       </c>
-      <c r="C59" s="33" t="s">
+      <c r="C59" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D59" s="34" t="s">
+      <c r="D59" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E59" s="33" t="s">
+      <c r="E59" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="20"/>
-      <c r="G59" s="21"/>
-      <c r="H59" s="25"/>
-    </row>
-    <row r="60" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="32">
+      <c r="F59" s="41"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="13"/>
+    </row>
+    <row r="60" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B60" s="15">
         <v>5</v>
       </c>
-      <c r="C60" s="33" t="s">
+      <c r="C60" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D60" s="34" t="s">
+      <c r="D60" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E60" s="33" t="s">
+      <c r="E60" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F60" s="20"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="25"/>
-    </row>
-    <row r="61" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="32">
+      <c r="F60" s="41"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="13"/>
+    </row>
+    <row r="61" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B61" s="15">
         <v>5</v>
       </c>
-      <c r="C61" s="33" t="s">
+      <c r="C61" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D61" s="34" t="s">
+      <c r="D61" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E61" s="33" t="s">
+      <c r="E61" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F61" s="20"/>
-      <c r="G61" s="21"/>
-      <c r="H61" s="25"/>
-    </row>
-    <row r="62" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F61" s="41"/>
+      <c r="G61" s="42"/>
+      <c r="H61" s="13"/>
+    </row>
+    <row r="62" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B62" s="5">
         <v>5</v>
       </c>
@@ -2278,11 +2235,11 @@
       <c r="E62" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F62" s="20"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="25"/>
-    </row>
-    <row r="63" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F62" s="41"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="13"/>
+    </row>
+    <row r="63" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B63" s="5">
         <v>5</v>
       </c>
@@ -2295,11 +2252,11 @@
       <c r="E63" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F63" s="20"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="25"/>
-    </row>
-    <row r="64" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F63" s="41"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="13"/>
+    </row>
+    <row r="64" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B64" s="5">
         <v>5</v>
       </c>
@@ -2312,11 +2269,11 @@
       <c r="E64" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F64" s="20"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="25"/>
-    </row>
-    <row r="65" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F64" s="41"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="13"/>
+    </row>
+    <row r="65" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B65" s="5">
         <v>5</v>
       </c>
@@ -2329,11 +2286,11 @@
       <c r="E65" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F65" s="20"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="25"/>
-    </row>
-    <row r="66" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F65" s="41"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="13"/>
+    </row>
+    <row r="66" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B66" s="5">
         <v>5</v>
       </c>
@@ -2346,11 +2303,11 @@
       <c r="E66" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F66" s="20"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="25"/>
-    </row>
-    <row r="67" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F66" s="41"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="13"/>
+    </row>
+    <row r="67" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B67" s="5">
         <v>5</v>
       </c>
@@ -2363,11 +2320,11 @@
       <c r="E67" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F67" s="20"/>
-      <c r="G67" s="21"/>
-      <c r="H67" s="25"/>
-    </row>
-    <row r="68" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F67" s="41"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="13"/>
+    </row>
+    <row r="68" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B68" s="5">
         <v>5</v>
       </c>
@@ -2380,11 +2337,11 @@
       <c r="E68" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F68" s="20"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="25"/>
-    </row>
-    <row r="69" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F68" s="41"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="13"/>
+    </row>
+    <row r="69" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B69" s="5">
         <v>5</v>
       </c>
@@ -2397,149 +2354,149 @@
       <c r="E69" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F69" s="22"/>
-      <c r="G69" s="23"/>
-      <c r="H69" s="26"/>
-    </row>
-    <row r="70" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="35">
+      <c r="F69" s="43"/>
+      <c r="G69" s="44"/>
+      <c r="H69" s="14"/>
+    </row>
+    <row r="70" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B70" s="18">
         <v>4</v>
       </c>
-      <c r="C70" s="36" t="s">
+      <c r="C70" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="37" t="s">
+      <c r="D70" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E70" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="G70" s="19"/>
-      <c r="H70" s="24"/>
-    </row>
-    <row r="71" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="35">
+      <c r="E70" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="G70" s="40"/>
+      <c r="H70" s="12"/>
+    </row>
+    <row r="71" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B71" s="18">
         <v>4</v>
       </c>
-      <c r="C71" s="36" t="s">
+      <c r="C71" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D71" s="37" t="s">
+      <c r="D71" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E71" s="36" t="s">
+      <c r="E71" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F71" s="20"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="25"/>
-    </row>
-    <row r="72" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="35">
+      <c r="F71" s="41"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="13"/>
+    </row>
+    <row r="72" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B72" s="18">
         <v>4</v>
       </c>
-      <c r="C72" s="36" t="s">
+      <c r="C72" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D72" s="37" t="s">
+      <c r="D72" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="36" t="s">
+      <c r="E72" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F72" s="20"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="25"/>
-    </row>
-    <row r="73" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="32">
+      <c r="F72" s="41"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="13"/>
+    </row>
+    <row r="73" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B73" s="15">
         <v>4</v>
       </c>
-      <c r="C73" s="33" t="s">
+      <c r="C73" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D73" s="34" t="s">
+      <c r="D73" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E73" s="33" t="s">
+      <c r="E73" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F73" s="20"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="25"/>
-    </row>
-    <row r="74" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="32">
+      <c r="F73" s="41"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="13"/>
+    </row>
+    <row r="74" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B74" s="15">
         <v>4</v>
       </c>
-      <c r="C74" s="33" t="s">
+      <c r="C74" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D74" s="34" t="s">
+      <c r="D74" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E74" s="33" t="s">
+      <c r="E74" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F74" s="20"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="25"/>
-    </row>
-    <row r="75" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="32">
+      <c r="F74" s="41"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="13"/>
+    </row>
+    <row r="75" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B75" s="15">
         <v>4</v>
       </c>
-      <c r="C75" s="33" t="s">
+      <c r="C75" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D75" s="34" t="s">
+      <c r="D75" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E75" s="33" t="s">
+      <c r="E75" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F75" s="20"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="25"/>
-    </row>
-    <row r="76" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="32">
+      <c r="F75" s="41"/>
+      <c r="G75" s="42"/>
+      <c r="H75" s="13"/>
+    </row>
+    <row r="76" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B76" s="15">
         <v>4</v>
       </c>
-      <c r="C76" s="33" t="s">
+      <c r="C76" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="34" t="s">
+      <c r="D76" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E76" s="33" t="s">
+      <c r="E76" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F76" s="20"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="25"/>
-    </row>
-    <row r="77" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="32">
+      <c r="F76" s="41"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="13"/>
+    </row>
+    <row r="77" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B77" s="15">
         <v>4</v>
       </c>
-      <c r="C77" s="33" t="s">
+      <c r="C77" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D77" s="34" t="s">
+      <c r="D77" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E77" s="33" t="s">
+      <c r="E77" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F77" s="20"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="25"/>
-    </row>
-    <row r="78" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F77" s="41"/>
+      <c r="G77" s="42"/>
+      <c r="H77" s="13"/>
+    </row>
+    <row r="78" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B78" s="5">
         <v>4</v>
       </c>
@@ -2552,11 +2509,11 @@
       <c r="E78" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F78" s="20"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="25"/>
-    </row>
-    <row r="79" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F78" s="41"/>
+      <c r="G78" s="42"/>
+      <c r="H78" s="13"/>
+    </row>
+    <row r="79" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B79" s="5">
         <v>4</v>
       </c>
@@ -2569,11 +2526,11 @@
       <c r="E79" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F79" s="20"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="25"/>
-    </row>
-    <row r="80" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F79" s="41"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="13"/>
+    </row>
+    <row r="80" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B80" s="5">
         <v>4</v>
       </c>
@@ -2586,11 +2543,11 @@
       <c r="E80" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F80" s="20"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="25"/>
-    </row>
-    <row r="81" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F80" s="41"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="13"/>
+    </row>
+    <row r="81" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B81" s="5">
         <v>4</v>
       </c>
@@ -2603,11 +2560,11 @@
       <c r="E81" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F81" s="20"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="25"/>
-    </row>
-    <row r="82" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F81" s="41"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="13"/>
+    </row>
+    <row r="82" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B82" s="5">
         <v>4</v>
       </c>
@@ -2620,11 +2577,11 @@
       <c r="E82" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F82" s="20"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="25"/>
-    </row>
-    <row r="83" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F82" s="41"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="13"/>
+    </row>
+    <row r="83" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B83" s="5">
         <v>4</v>
       </c>
@@ -2637,11 +2594,11 @@
       <c r="E83" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F83" s="20"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="25"/>
-    </row>
-    <row r="84" spans="2:8" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F83" s="41"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="13"/>
+    </row>
+    <row r="84" spans="2:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B84" s="5">
         <v>4</v>
       </c>
@@ -2654,9 +2611,9 @@
       <c r="E84" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F84" s="22"/>
-      <c r="G84" s="23"/>
-      <c r="H84" s="26"/>
+      <c r="F84" s="43"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="8">
